--- a/proyectos/demoqa-ui/reportes/escenarios.xlsx
+++ b/proyectos/demoqa-ui/reportes/escenarios.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Escenarios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Escenarios'!$A$1:$N$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Escenarios'!$A$1:$N$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +49,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -62,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -71,6 +76,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2703,8 +2709,968 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ESC-0033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Alerts</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Alert simple</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Disparar el alert simple</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>El mensaje del alert es 'You clicked a button'</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>tests/ui/test_alerts.py::test_alert_simple[chromium]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ESC-0034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Alerts</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Aceptar el confirm</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>El mensaje es 'Do you confirm action?' y el resultado 'You selected Ok'</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>tests/ui/test_alerts.py::test_confirm_aceptar[chromium]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ESC-0035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Alerts</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Cancelar el confirm</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>El resultado es 'You selected Cancel'</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>tests/ui/test_alerts.py::test_confirm_cancelar[chromium]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ESC-0036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Alerts</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Responder el prompt con un texto</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>El resultado es 'You entered &lt;texto&gt;'</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>tests/ui/test_alerts.py::test_prompt[chromium]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ESC-0037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Buttons</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Tipos de clic</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Hacer doble clic en 'Double Click Me'</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Se muestra el mensaje 'You have done a double click'</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>tests/ui/test_buttons.py::test_doble_clic[chromium]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ESC-0038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Buttons</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Tipos de clic</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Hacer clic derecho en 'Right Click Me'</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Se muestra el mensaje 'You have done a right click'</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>tests/ui/test_buttons.py::test_clic_derecho[chromium]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ESC-0039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Buttons</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Tipos de clic</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Hacer clic simple en el botón 'Click Me' que no tiene doble clic ni clic derecho</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Se muestra el mensaje 'You have done a dynamic click'</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>tests/ui/test_buttons.py::test_clic_simple[chromium]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ESC-0040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Text Box</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Completar formulario</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Completar los 4 campos con datos válidos y enviar</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>El resultado muestra nombre - email y ambas direcciones tal como se escribieron</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>tests/ui/test_text_box.py::test_completar_formulario[chromium]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ESC-0041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Text Box</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Completar formulario</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Enviar con un email sin formato válido</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>El campo Email se marca con error y el resultado no incluye la línea de Email</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>tests/ui/test_text_box.py::test_email_invalido[chromium]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ESC-0042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Text Box</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Completar formulario</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Enviar el formulario sin completar ningún campo</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>No se agrega ninguna línea de resultado</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>tests/ui/test_text_box.py::test_enviar_vacio[chromium]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ESC-0043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Web Tables</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Agregar registro</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Completar el formulario con datos válidos y enviarlo</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>La tabla muestra una fila nueva con los datos ingresados</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>tests/ui/test_webtables.py::test_agregar_registro[chromium]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ESC-0044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Web Tables</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Agregar registro</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Enviar el formulario con un email sin formato válido</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>El formulario no se envía: el modal permanece abierto y no se agrega ninguna fila</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>tests/ui/test_webtables.py::test_agregar_registro_email_invalido[chromium]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ESC-0045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Web Tables</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Editar registro</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Editar el apellido de un registro existente</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>La fila muestra el apellido nuevo y conserva el resto de los datos</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>tests/ui/test_webtables.py::test_editar_registro[chromium]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ESC-0046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Web Tables</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Eliminar registro</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Eliminar un registro existente</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>La fila deja de estar en la tabla</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>tests/ui/test_webtables.py::test_eliminar_registro[chromium]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ESC-0047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Web Tables</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Buscar</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Buscar por un texto que coincide con una sola fila (email)</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Solo queda visible la fila que coincide con la búsqueda</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>NO_EJECUTADO</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:05:19</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>tests/ui/test_webtables.py::test_buscar[chromium]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N33"/>
+  <autoFilter ref="A1:N48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>